--- a/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>UNION DE NUEVOS INTELIGENTES - UNI CUSCO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.52969</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.95189999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>214</v>
-      </c>
-      <c r="J2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.52969</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.9519</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>REVOLUCIONARIA SANTA ROSA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.535614</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.925146</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1822</v>
-      </c>
-      <c r="J3" t="n">
-        <v>83</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.535614</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.925146</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1822</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>ORDESO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.52413</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.96211</v>
-      </c>
-      <c r="I4" t="n">
-        <v>285</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.52413</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.96211</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>MARIA TRINIDAD ENRIQUEZ</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.53171</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.95653</v>
-      </c>
-      <c r="I5" t="n">
-        <v>269</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.53171</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.95653</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.52984</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.94674000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>242</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.52984</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.94674</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>MARIA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.5248</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.96283</v>
-      </c>
-      <c r="I7" t="n">
-        <v>493</v>
-      </c>
-      <c r="J7" t="n">
-        <v>28</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.5248</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.96283</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>50032 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.52846</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.95397</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1210</v>
-      </c>
-      <c r="J8" t="n">
-        <v>56</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.52846</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.95397</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>50731 NUESTR SEÑORA DE LA NATIVIDAD DE PROGRESO / 50731 NUESTRA SEÑORA DE LA NATIVIDAD DE PROGRESO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.52806</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.96165000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>388</v>
-      </c>
-      <c r="J9" t="n">
-        <v>19</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.52806</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.96165</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>URIEL GARCIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.5343</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.95780000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1996</v>
-      </c>
-      <c r="J10" t="n">
-        <v>97</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.5343</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.9578</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.533</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.9601</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>100</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.533</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.9601</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.53051</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.94752</v>
-      </c>
-      <c r="I12" t="n">
-        <v>339</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.53051</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.94752</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>ARTURO PALOMINO RODRIGUEZ</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.53259</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.95244</v>
-      </c>
-      <c r="I13" t="n">
-        <v>642</v>
-      </c>
-      <c r="J13" t="n">
-        <v>33</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.53259</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.95244</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>51021</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.52451</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.95822</v>
-      </c>
-      <c r="I14" t="n">
-        <v>361</v>
-      </c>
-      <c r="J14" t="n">
-        <v>16</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.52451</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.95822</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>51014 ROMERITOS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.5284</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.96526</v>
-      </c>
-      <c r="I15" t="n">
-        <v>592</v>
-      </c>
-      <c r="J15" t="n">
-        <v>37</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.5284</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.96526</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>51045 VELASCO ASTETE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.53719</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.94828</v>
-      </c>
-      <c r="I16" t="n">
-        <v>381</v>
-      </c>
-      <c r="J16" t="n">
-        <v>19</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.53719</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.94828</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>50025 DANIEL ESTRADA PEREZ</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.52461</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.96225</v>
-      </c>
-      <c r="I17" t="n">
-        <v>840</v>
-      </c>
-      <c r="J17" t="n">
-        <v>41</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.52461</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.96225</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>OLIMPICO PERUANO</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.5264</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.95740000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>202</v>
-      </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.5264</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.9574</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.53072</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.95968999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1111</v>
-      </c>
-      <c r="J19" t="n">
-        <v>51</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.53072</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.95969</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>SANTA ANA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-13.52877</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.94901</v>
-      </c>
-      <c r="I20" t="n">
-        <v>855</v>
-      </c>
-      <c r="J20" t="n">
-        <v>47</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-13.52877</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.94901</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>DOMINGO SAVIO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-13.52709</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.96623</v>
-      </c>
-      <c r="I21" t="n">
-        <v>442</v>
-      </c>
-      <c r="J21" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-13.52709</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.96623</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>GALILEO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-13.52188</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.97031</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2084</v>
-      </c>
-      <c r="J22" t="n">
-        <v>42</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-13.52188</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.97031</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-13.52174</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.97225</v>
-      </c>
-      <c r="I23" t="n">
-        <v>215</v>
-      </c>
-      <c r="J23" t="n">
-        <v>16</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-13.52174</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.97225</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-13.534027</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-71.957987</v>
-      </c>
-      <c r="I24" t="n">
-        <v>222</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-13.534027</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-71.957987</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>MILLENNIUM</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-13.528248</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-71.956243</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1725</v>
-      </c>
-      <c r="J25" t="n">
-        <v>49</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-13.528248</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-71.956243</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>146917</t>
+          <t>148898</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UNION DE NUEVOS INTELIGENTES - UNI CUSCO</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.52969</t>
+          <t>-13.52984</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.9519</t>
+          <t>-71.94674</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>148068</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>REVOLUCIONARIA SANTA ROSA</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.535614</t>
+          <t>-13.533</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.925146</t>
+          <t>-71.9601</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>148879</t>
+          <t>148884</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ORDESO</t>
+          <t>MARIA TRINIDAD ENRIQUEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.52413</t>
+          <t>-13.53171</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.96211</t>
+          <t>-71.95653</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>148884</t>
+          <t>148879</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MARIA TRINIDAD ENRIQUEZ</t>
+          <t>ORDESO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.53171</t>
+          <t>-13.52413</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.95653</t>
+          <t>-71.96211</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>148898</t>
+          <t>149077</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>OLIMPICO PERUANO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.52984</t>
+          <t>-13.5264</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.94674</t>
+          <t>-71.9574</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>148959</t>
+          <t>149039</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MARIA DE LA MERCED</t>
+          <t>51021</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.5248</t>
+          <t>-13.52451</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.96283</t>
+          <t>-71.95822</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>148964</t>
+          <t>599433</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50032 MIGUEL GRAU SEMINARIO</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.52846</t>
+          <t>-13.52174</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.95397</t>
+          <t>-71.97225</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>148978</t>
+          <t>146917</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50731 NUESTR SEÑORA DE LA NATIVIDAD DE PROGRESO / 50731 NUESTRA SEÑORA DE LA NATIVIDAD DE PROGRESO</t>
+          <t>UNION DE NUEVOS INTELIGENTES - UNI CUSCO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.52806</t>
+          <t>-13.52969</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.96165</t>
+          <t>-71.9519</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>148983</t>
+          <t>148978</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>URIEL GARCIA</t>
+          <t>50731 NUESTR SEÑORA DE LA NATIVIDAD DE PROGRESO / 50731 NUESTRA SEÑORA DE LA NATIVIDAD DE PROGRESO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.5343</t>
+          <t>-13.52806</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.9578</t>
+          <t>-71.96165</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>148997</t>
+          <t>149058</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>51045 VELASCO ASTETE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.533</t>
+          <t>-13.53719</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.9601</t>
+          <t>-71.94828</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>149015</t>
+          <t>149416</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
+          <t>DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.53051</t>
+          <t>-13.52709</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.94752</t>
+          <t>-71.96623</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>149020</t>
+          <t>149015</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ARTURO PALOMINO RODRIGUEZ</t>
+          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.53259</t>
+          <t>-13.53051</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.95244</t>
+          <t>-71.94752</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>149039</t>
+          <t>644402</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51021</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.52451</t>
+          <t>-13.534027</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.95822</t>
+          <t>-71.957987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>149044</t>
+          <t>148959</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51014 ROMERITOS</t>
+          <t>MARIA DE LA MERCED</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.5284</t>
+          <t>-13.5248</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.96526</t>
+          <t>-71.96283</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>493</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>149058</t>
+          <t>149020</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51045 VELASCO ASTETE</t>
+          <t>ARTURO PALOMINO RODRIGUEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.53719</t>
+          <t>-13.53259</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.94828</t>
+          <t>-71.95244</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>642</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>149063</t>
+          <t>149044</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>50025 DANIEL ESTRADA PEREZ</t>
+          <t>51014 ROMERITOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.52461</t>
+          <t>-13.5284</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.96225</t>
+          <t>-71.96526</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>592</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>149063</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OLIMPICO PERUANO</t>
+          <t>50025 DANIEL ESTRADA PEREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.5264</t>
+          <t>-13.52461</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.9574</t>
+          <t>-71.96225</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>840</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>149261</t>
+          <t>149421</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>GALILEO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.53072</t>
+          <t>-13.52188</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.95969</t>
+          <t>-71.97031</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>149416</t>
+          <t>911202</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DOMINGO SAVIO</t>
+          <t>MILLENNIUM</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.52709</t>
+          <t>-13.528248</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.96623</t>
+          <t>-71.956243</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>149421</t>
+          <t>149261</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GALILEO</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.52188</t>
+          <t>-13.53072</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.97031</t>
+          <t>-71.95969</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>599433</t>
+          <t>148964</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>50032 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.52174</t>
+          <t>-13.52846</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.97225</t>
+          <t>-71.95397</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>644402</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>REVOLUCIONARIA SANTA ROSA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.534027</t>
+          <t>-13.535614</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.957987</t>
+          <t>-71.925146</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>911202</t>
+          <t>148983</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MILLENNIUM</t>
+          <t>URIEL GARCIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.528248</t>
+          <t>-13.5343</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.956243</t>
+          <t>-71.9578</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">

--- a/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>148898</t>
+          <t>911202</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>MILLENNIUM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.52984</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.94674</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-13.528248</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.956243</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>148997</t>
+          <t>644402</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.533</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.9601</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>-13.534027</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-71.957987</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>148884</t>
+          <t>599433</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MARIA TRINIDAD ENRIQUEZ</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.53171</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.95653</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-13.52174</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.97225</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>148879</t>
+          <t>149421</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ORDESO</t>
+          <t>GALILEO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.52413</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.96211</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-13.52188</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-71.97031</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>149416</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OLIMPICO PERUANO</t>
+          <t>DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.5264</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.9574</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-13.52709</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.96623</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>149039</t>
+          <t>149280</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51021</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.52451</t>
+          <t>855</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.95822</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>-13.52877</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.94901</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>599433</t>
+          <t>149261</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.52174</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.97225</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-13.53072</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.95969</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>146917</t>
+          <t>149077</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UNION DE NUEVOS INTELIGENTES - UNI CUSCO</t>
+          <t>OLIMPICO PERUANO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.52969</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.9519</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-13.5264</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.9574</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>148978</t>
+          <t>149063</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50731 NUESTR SEÑORA DE LA NATIVIDAD DE PROGRESO / 50731 NUESTRA SEÑORA DE LA NATIVIDAD DE PROGRESO</t>
+          <t>50025 DANIEL ESTRADA PEREZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.52806</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.96165</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-13.52461</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.96225</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>-13.53719</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>-71.94828</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>149416</t>
+          <t>149044</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DOMINGO SAVIO</t>
+          <t>51014 ROMERITOS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.52709</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.96623</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-13.5284</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.96526</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>149015</t>
+          <t>149039</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
+          <t>51021</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.53051</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.94752</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-13.52451</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.95822</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>644402</t>
+          <t>149020</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>ARTURO PALOMINO RODRIGUEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.534027</t>
+          <t>642</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.957987</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-13.53259</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.95244</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>148959</t>
+          <t>149015</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MARIA DE LA MERCED</t>
+          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.5248</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.96283</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>-13.53051</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-71.94752</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>149020</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ARTURO PALOMINO RODRIGUEZ</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.53259</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.95244</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>-13.533</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-71.9601</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>149044</t>
+          <t>148983</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51014 ROMERITOS</t>
+          <t>URIEL GARCIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.5284</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.96526</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>-13.5343</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-71.9578</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>149063</t>
+          <t>148978</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50025 DANIEL ESTRADA PEREZ</t>
+          <t>50731 NUESTR SEÑORA DE LA NATIVIDAD DE PROGRESO / 50731 NUESTRA SEÑORA DE LA NATIVIDAD DE PROGRESO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.52461</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.96225</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>-13.52806</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-71.96165</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>149421</t>
+          <t>148964</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GALILEO</t>
+          <t>50032 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.52188</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.97031</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>-13.52846</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-71.95397</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>149280</t>
+          <t>148959</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>MARIA DE LA MERCED</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.52877</t>
+          <t>493</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.94901</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>-13.5248</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-71.96283</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>911202</t>
+          <t>148898</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MILLENNIUM</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.528248</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.956243</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>-13.52984</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-71.94674</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>149261</t>
+          <t>148884</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>MARIA TRINIDAD ENRIQUEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.53072</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.95969</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>-13.53171</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-71.95653</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>148964</t>
+          <t>148879</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50032 MIGUEL GRAU SEMINARIO</t>
+          <t>ORDESO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.52846</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.95397</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>-13.52413</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-71.96211</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>1822</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>-13.535614</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-71.925146</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>83</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>148983</t>
+          <t>146917</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>URIEL GARCIA</t>
+          <t>UNION DE NUEVOS INTELIGENTES - UNI CUSCO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.5343</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.9578</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>-13.52969</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-71.9519</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">

--- a/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-WANCHAQ.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
